--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mediabrut_a_2023_metropolitana.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mediabrut_a_2023_metropolitana.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:56</t>
+    <t xml:space="preserve">2026-09-24 01:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -845,19 +845,19 @@
         <v>25</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.18</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>51</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="16">
@@ -868,19 +868,19 @@
         <v>25</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.62</v>
+        <v>-0.55</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>51</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="17">
@@ -891,19 +891,19 @@
         <v>25</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>51</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="18">
